--- a/Farm/Assets/Configs/seed.xlsx
+++ b/Farm/Assets/Configs/seed.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
   <si>
     <t>#seed.xlsx</t>
   </si>
@@ -64,6 +64,9 @@
     <t>收获数量</t>
   </si>
   <si>
+    <t>售价</t>
+  </si>
+  <si>
     <t>图标</t>
   </si>
   <si>
@@ -101,6 +104,9 @@
   </si>
   <si>
     <t>bonus_amount</t>
+  </si>
+  <si>
+    <t>sell_price</t>
   </si>
   <si>
     <t>icon</t>
@@ -1050,32 +1056,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="4" max="4" width="15.1111111111111" style="1" customWidth="1"/>
     <col min="5" max="5" width="16.3333333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="31.3333333333333" style="1" customWidth="1"/>
     <col min="7" max="7" width="21.5555555555556" style="1" customWidth="1"/>
-    <col min="8" max="8" width="13.8888888888889" style="1" customWidth="1"/>
+    <col min="8" max="9" width="13.8888888888889" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -1103,71 +1109,80 @@
       <c r="I6" t="s">
         <v>11</v>
       </c>
+      <c r="J6" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
+        <v>14</v>
+      </c>
+      <c r="C7" t="s">
         <v>13</v>
       </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
       <c r="D7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I7" t="s">
         <v>13</v>
       </c>
+      <c r="J7" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G8" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I8" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="J8" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:10">
       <c r="A9">
         <v>1000</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C9">
         <v>1</v>
@@ -1179,16 +1194,19 @@
         <v>0.4</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I9" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
